--- a/Tekster og billeder til Keramikruten.xlsx
+++ b/Tekster og billeder til Keramikruten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elisabethtejlmand/Documents/GitHub/guide-til-middelfart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADC1277-C0A4-4440-8205-9332FFCAEE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7605A46E-FA7F-9845-B8FA-78692EC70F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8880" yWindow="4360" windowWidth="28240" windowHeight="17240" xr2:uid="{02FFEFA7-C0A6-4249-8E30-DEFBC5A1D164}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -222,6 +222,48 @@
   </si>
   <si>
     <t>9.722185</t>
+  </si>
+  <si>
+    <t>livsnyderne</t>
+  </si>
+  <si>
+    <t>Livsnyderne</t>
+  </si>
+  <si>
+    <t>Havnefronten</t>
+  </si>
+  <si>
+    <t>Skal du op og sidde?</t>
+  </si>
+  <si>
+    <t>I vandet omkring Middelfart boltrer en af Danmarks største bestande af hvaler sig; nemlig den lille, legesyge marsvin. Hold godt øje, så ser du sikkert en finne bryde vandoverfladen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det er svært at vælge det bedste spisested - for smag og behag er forskellig. Guldkronen på Gl. Torv er specialister i den hyggelige atmosfære og dansk smørebrød, mens Cafe Razz er indbegrebet af traditionel cafemad. Længere nede ad Algade finder du skønne spisesteder som perler på en snor. Google Maps kan guide dig. </t>
+  </si>
+  <si>
+    <t>55.506345</t>
+  </si>
+  <si>
+    <t>9.732167</t>
+  </si>
+  <si>
+    <t>Stoflig sanselighed</t>
+  </si>
+  <si>
+    <t>Den dragende dråbe</t>
+  </si>
+  <si>
+    <t>De sidste værker er i parken ved Clay Keramikmuseum</t>
+  </si>
+  <si>
+    <t>Gå gennem Nytorvs port til Havnegade og bevæg dig mod syd langs vandet.</t>
+  </si>
+  <si>
+    <t>• • • https://maps.app.goo.gl/Wqa6YgPdz8Hgc7Zk9?g_st=ic</t>
+  </si>
+  <si>
+    <t>Tag en lille omvej forbi Gl. Havns karakteriske røde værtsbygninger, hvor man har bygget smakkejoller og klinkbygning, der er klasificeret som Verdenskulturarv af UNESCO.</t>
   </si>
 </sst>
 </file>
@@ -297,7 +339,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -312,6 +354,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -656,8 +699,8 @@
     <col min="6" max="6" width="26.33203125" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" customWidth="1"/>
+    <col min="10" max="11" width="21" customWidth="1"/>
     <col min="12" max="12" width="42.83203125" customWidth="1"/>
     <col min="14" max="14" width="48.5" customWidth="1"/>
     <col min="15" max="15" width="33.83203125" customWidth="1"/>
@@ -742,6 +785,9 @@
       <c r="H2" s="9" t="s">
         <v>60</v>
       </c>
+      <c r="I2" t="s">
+        <v>70</v>
+      </c>
       <c r="J2" s="6" t="s">
         <v>40</v>
       </c>
@@ -786,8 +832,14 @@
       <c r="H3" s="9" t="s">
         <v>54</v>
       </c>
+      <c r="I3" t="s">
+        <v>69</v>
+      </c>
       <c r="J3" s="6" t="s">
         <v>41</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>25</v>
@@ -890,7 +942,9 @@
       <c r="N5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="3"/>
+      <c r="O5" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="P5" t="s">
         <v>44</v>
       </c>
@@ -898,22 +952,54 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="17" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+    <row r="6" spans="1:17" ht="137" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2001</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="N6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
@@ -1124,6 +1210,7 @@
     <hyperlink ref="N2" r:id="rId1" xr:uid="{425307A9-2A13-124F-A947-E6A946E98065}"/>
     <hyperlink ref="N4" r:id="rId2" xr:uid="{D5DEB3DA-93D1-6C4B-B6EE-A954DA83D819}"/>
     <hyperlink ref="N5" r:id="rId3" xr:uid="{D082706D-F5AF-F445-B8F7-AAB60CDD41FD}"/>
+    <hyperlink ref="N6" r:id="rId4" display="https://maps.app.goo.gl/Wqa6YgPdz8Hgc7Zk9?g_st=ic" xr:uid="{F4BBC5C5-A02A-2A43-86DE-EBFD25438B5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Tekster og billeder til Keramikruten.xlsx
+++ b/Tekster og billeder til Keramikruten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elisabethtejlmand/Documents/GitHub/guide-til-middelfart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7605A46E-FA7F-9845-B8FA-78692EC70F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5467E3-5446-2B4F-8962-0DFA505D00F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8880" yWindow="4360" windowWidth="28240" windowHeight="17240" xr2:uid="{02FFEFA7-C0A6-4249-8E30-DEFBC5A1D164}"/>
+    <workbookView xWindow="7220" yWindow="3120" windowWidth="28240" windowHeight="17240" xr2:uid="{02FFEFA7-C0A6-4249-8E30-DEFBC5A1D164}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -101,9 +101,6 @@
     <t>https://maps.app.goo.gl/8hmEXx7BMGceXriw7?g_st=ic</t>
   </si>
   <si>
-    <t>Gå nedad stien gennem kirkegaarden.</t>
-  </si>
-  <si>
     <t>Værket er placeret ved et afvandingssystem, der under voldsomme regnskyl holder kældre og stuer tørre i den gamle bydel, hvor kloarkerne førhen havde svært ved at følge med. Regnvandet ledes ovenpå de gamle brosten ned til havnen, hvor det forsvinder ud i Lillebælt.</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>Du står ved Rådhuset, bygget i 2017 som det første byggeri i Danmark certificeret med DGNB platin + diamant. Danmarks hidtil højeste score inden for miljømæssige kvaliteter.</t>
   </si>
   <si>
-    <t>Hvad er der mon på færdie mellem de 3 figurer?</t>
-  </si>
-  <si>
     <t>To der er helt deres egne</t>
   </si>
   <si>
@@ -264,6 +258,42 @@
   </si>
   <si>
     <t>Tag en lille omvej forbi Gl. Havns karakteriske røde værtsbygninger, hvor man har bygget smakkejoller og klinkbygning, der er klasificeret som Verdenskulturarv af UNESCO.</t>
+  </si>
+  <si>
+    <t>Altings_Toeven_Per_Ahlmann_2017.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gå op ad trappen og drej til venstre ad Kongebrovejen. </t>
+  </si>
+  <si>
+    <t>Rook_takes_Bishop_Magne_Furuholmen_2017.jpeg</t>
+  </si>
+  <si>
+    <t>Skulpturgruppe_Betty_Engholm_2000.jpeg</t>
+  </si>
+  <si>
+    <t>Livsnyderne_Betty_Engholm_2001.jpeg</t>
+  </si>
+  <si>
+    <t>Krukke_Gunhild_Rudjord_2017.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De to høje figurer er placeret overfor hinanden i et mønster af firkanter, der leder tankerne hen på brikker på et skakbrædt. Værkets skaber billedkunstner Magne Furuholmen er da også optaget af print, bogstaver og grafik. Ifølge Clay må publikum gerne røre figurerne. Det sammen med placeringen ved Sct. Nikolai Kirke trækker i min optik både byrum og os som gæster ind i værket. </t>
+  </si>
+  <si>
+    <t>Hvad er der mon på færde mellem de 3 figurer?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De 3 figurer har en samtale i ord og krop, men hvad taler de om, og kan de forlæse hinanden i en forandring? Igen et værk der trækker os - og måske også rådhuset? - med ind. Værkets skaber Betty Engholm er kendt for sin sanselige skulpturer. Clay skrive rom det: Engholm benytter en særlig modelleringsteknik, når hun bygger sine skulpturer op. Hun kalder det haletudseteknik. Det vil sige, at hun bruger klumper af ler, der formes som haletudser, som trykkes sammen, efterhånden som hun bygger formen op. </t>
+  </si>
+  <si>
+    <t>Betty Enghoms sanselighed i hendes værker kommer også til udtryk i dette værk, der hedder Livsnyderne. Det er som om, de to liggende figurer er smeltet sammen med bænken under dem, og hvem kan ikke relaterer til følelsen af at sommerferiens liggestol og ens krop bliver ét? Har du en favoritstol, der kan være svær at komme op ad en gangen imellem?</t>
+  </si>
+  <si>
+    <t>Dette værk er skabt ved hjælp af en slags kødhakker og tyngdekraften. Per Ahlmanns dragende skulptur lokker på lang afstand med sin vekslen mellem det formfuldendte og det uorganiserede, rustikke.  Dråben er skabt ved hjælp af en ekstruder (en maskine, der fungerer ligesom en kødhakker), der har presset leret ud til et rør. Understøttet af en slags galge er røret blevet hængt op, således at tyngdekraften kunne hjælpe med i formningen af dråben. Bemærk galgen har efterladt et aftryk øverst.  Det er en detalje, som Ahlmann er særligt glad for, da det vidner om en tidslighed, et før og et efter – en symbolik, der kobler sig smukt til kirkegården.</t>
+  </si>
+  <si>
+    <t>Krukke efterligner roen på kirkegården med sin majestætiske fremtoning, og hviler i sig selv uden at være anmassende. Det er i glasuren, at værket træder frem. Her er både noget genkendeligt og noget, der leder fantasien på vej, og bliver dermed ifølge kunstneren et billede på genopstandelsen. Værkets skaber norske Gunhild Rudjord mestrer arbejdet med de ofte ukontrollable glasurer til perfektion.</t>
   </si>
 </sst>
 </file>
@@ -690,18 +720,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7CA198-C529-0F4A-92E2-0CE00827A239}">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="8.6640625" customWidth="1"/>
     <col min="3" max="3" width="19.5" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
     <col min="6" max="6" width="26.33203125" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="10" max="11" width="21" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="35.83203125" customWidth="1"/>
     <col min="12" max="12" width="42.83203125" customWidth="1"/>
+    <col min="13" max="13" width="38.6640625" customWidth="1"/>
     <col min="14" max="14" width="48.5" customWidth="1"/>
     <col min="15" max="15" width="33.83203125" customWidth="1"/>
     <col min="17" max="17" width="32" customWidth="1"/>
@@ -754,13 +787,13 @@
         <v>16</v>
       </c>
       <c r="P1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="103" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="273" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -780,51 +813,57 @@
         <v>18</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>73</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="O2" t="s">
-        <v>20</v>
+      <c r="O2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="86" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="171" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3">
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3">
         <v>2017</v>
       </c>
-      <c r="F3" t="s">
-        <v>18</v>
+      <c r="F3" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>53</v>
@@ -832,46 +871,52 @@
       <c r="H3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>49</v>
+      <c r="I3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="69" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="222" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B4" s="4">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3">
-        <v>2017</v>
+        <v>2000</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>55</v>
@@ -880,130 +925,142 @@
         <v>56</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="L4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="N4" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="137" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:17" ht="154" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="B5" s="4">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E5" s="3">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>58</v>
+        <v>65</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="L5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="N5" s="5" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="137" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="171" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="B6" s="4">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2001</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>63</v>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>2017</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>71</v>
+      <c r="J6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="P6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1037,7 +1094,7 @@
     </row>
     <row r="9" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="7"/>
+      <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1105,7 +1162,7 @@
     </row>
     <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="3"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1122,7 +1179,7 @@
     </row>
     <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+      <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1154,8 +1211,8 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
     </row>
-    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -1188,31 +1245,17 @@
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="N2" r:id="rId1" xr:uid="{425307A9-2A13-124F-A947-E6A946E98065}"/>
-    <hyperlink ref="N4" r:id="rId2" xr:uid="{D5DEB3DA-93D1-6C4B-B6EE-A954DA83D819}"/>
-    <hyperlink ref="N5" r:id="rId3" xr:uid="{D082706D-F5AF-F445-B8F7-AAB60CDD41FD}"/>
-    <hyperlink ref="N6" r:id="rId4" display="https://maps.app.goo.gl/Wqa6YgPdz8Hgc7Zk9?g_st=ic" xr:uid="{F4BBC5C5-A02A-2A43-86DE-EBFD25438B5E}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{D5DEB3DA-93D1-6C4B-B6EE-A954DA83D819}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{D082706D-F5AF-F445-B8F7-AAB60CDD41FD}"/>
+    <hyperlink ref="N5" r:id="rId4" display="https://maps.app.goo.gl/Wqa6YgPdz8Hgc7Zk9?g_st=ic" xr:uid="{F4BBC5C5-A02A-2A43-86DE-EBFD25438B5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="G5:H5" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>